--- a/target_df.xlsx
+++ b/target_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="213">
   <si>
     <t>Kürzel (LongName)</t>
   </si>
@@ -166,6 +166,12 @@
     <t>RRG</t>
   </si>
   <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>TRHa</t>
+  </si>
+  <si>
     <t>AGS</t>
   </si>
   <si>
@@ -346,6 +352,15 @@
     <t xml:space="preserve">Reinigungsraum Geschoss </t>
   </si>
   <si>
+    <t>Aussennutzfläche</t>
+  </si>
+  <si>
+    <t>Aussenverkehrsfläche</t>
+  </si>
+  <si>
+    <t>Treppenhaus aussen</t>
+  </si>
+  <si>
     <t>Aussengeräteraum Sport</t>
   </si>
   <si>
@@ -421,6 +436,9 @@
     <t>Hausdienst</t>
   </si>
   <si>
+    <t>Sonstige Umgebung</t>
+  </si>
+  <si>
     <t>Sportbereich</t>
   </si>
   <si>
@@ -430,9 +448,6 @@
     <t>VF</t>
   </si>
   <si>
-    <t>ANF</t>
-  </si>
-  <si>
     <t>AGF</t>
   </si>
   <si>
@@ -569,6 +584,15 @@
   </si>
   <si>
     <t>Hausdienst_RRG</t>
+  </si>
+  <si>
+    <t>Sonstige Umgebung_ANF</t>
+  </si>
+  <si>
+    <t>Sonstige Umgebung_AVF</t>
+  </si>
+  <si>
+    <t>Sonstige Umgebung_TRHa</t>
   </si>
   <si>
     <t>Sportbereich_AGS</t>
@@ -986,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1020,16 +1044,16 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1037,13 +1061,13 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1051,16 +1075,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1068,16 +1092,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1085,16 +1109,16 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1102,10 +1126,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
@@ -1117,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H7">
         <v>390</v>
@@ -1128,13 +1152,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>10.4</v>
@@ -1143,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H8">
         <v>16</v>
@@ -1154,16 +1178,16 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1171,16 +1195,16 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1188,13 +1212,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G11" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1202,10 +1226,10 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
@@ -1217,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H12">
         <v>400</v>
@@ -1228,19 +1252,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H13">
         <v>54</v>
@@ -1251,10 +1275,10 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
@@ -1266,7 +1290,7 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H14">
         <v>300</v>
@@ -1277,10 +1301,10 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D15" t="s">
         <v>16</v>
@@ -1292,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H15">
         <v>12</v>
@@ -1303,16 +1327,16 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1320,10 +1344,10 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
         <v>16</v>
@@ -1332,7 +1356,7 @@
         <v>10.1</v>
       </c>
       <c r="G17" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1340,10 +1364,10 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
         <v>16</v>
@@ -1352,7 +1376,7 @@
         <v>10.1</v>
       </c>
       <c r="G18" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1360,13 +1384,13 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E19">
         <v>1.2</v>
@@ -1375,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H19">
         <v>72</v>
@@ -1386,13 +1410,13 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E20">
         <v>1.2</v>
@@ -1401,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H20">
         <v>54</v>
@@ -1412,13 +1436,13 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E21">
         <v>2.1</v>
@@ -1427,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H21">
         <v>18</v>
@@ -1438,13 +1462,13 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E22">
         <v>3.8</v>
@@ -1453,7 +1477,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H22">
         <v>55</v>
@@ -1464,13 +1488,13 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E23">
         <v>4.4</v>
@@ -1479,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H23">
         <v>7</v>
@@ -1490,13 +1514,13 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E24">
         <v>4.4</v>
@@ -1505,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H24">
         <v>4</v>
@@ -1516,13 +1540,13 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E25">
         <v>4.3</v>
@@ -1531,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H25">
         <v>7</v>
@@ -1542,13 +1566,13 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E26">
         <v>1.5</v>
@@ -1557,7 +1581,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H26">
         <v>72</v>
@@ -1568,13 +1592,13 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E27">
         <v>7.1</v>
@@ -1583,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1594,13 +1618,13 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E28">
         <v>7.2</v>
@@ -1609,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H28">
         <v>108</v>
@@ -1620,13 +1644,13 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E29">
         <v>7.1</v>
@@ -1635,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H29">
         <v>2.5</v>
@@ -1646,13 +1670,13 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E30">
         <v>7.1</v>
@@ -1661,7 +1685,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H30">
         <v>2.5</v>
@@ -1672,13 +1696,13 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E31">
         <v>7.1</v>
@@ -1687,7 +1711,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H31">
         <v>2.5</v>
@@ -1698,13 +1722,13 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E32">
         <v>7.1</v>
@@ -1713,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H32">
         <v>2.5</v>
@@ -1724,13 +1748,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E33">
         <v>7.1</v>
@@ -1739,7 +1763,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H33">
         <v>3</v>
@@ -1750,13 +1774,13 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D34" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E34">
         <v>8.300000000000001</v>
@@ -1765,7 +1789,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H34">
         <v>25</v>
@@ -1776,13 +1800,13 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E35">
         <v>8.5</v>
@@ -1791,7 +1815,7 @@
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H35">
         <v>90</v>
@@ -1802,13 +1826,13 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E36">
         <v>8.1</v>
@@ -1817,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H36">
         <v>150</v>
@@ -1828,13 +1852,13 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E37">
         <v>8.300000000000001</v>
@@ -1843,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H37">
         <v>40</v>
@@ -1854,19 +1878,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -1877,13 +1901,13 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D39" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E39">
         <v>4.1</v>
@@ -1892,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H39">
         <v>20</v>
@@ -1903,13 +1927,13 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E40">
         <v>7.3</v>
@@ -1918,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H40">
         <v>12</v>
@@ -1929,13 +1953,13 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E41">
         <v>7.2</v>
@@ -1944,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H41">
         <v>12</v>
@@ -1955,13 +1979,13 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D42" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E42">
         <v>7.1</v>
@@ -1970,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H42">
         <v>25</v>
@@ -1981,13 +2005,13 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E43">
         <v>7.1</v>
@@ -1996,7 +2020,7 @@
         <v>3</v>
       </c>
       <c r="G43" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H43">
         <v>18</v>
@@ -2007,178 +2031,151 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
-      </c>
-      <c r="E44">
-        <v>4.1</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G44" t="s">
-        <v>185</v>
-      </c>
-      <c r="H44">
-        <v>15</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
-      </c>
-      <c r="E45">
-        <v>9.1</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>186</v>
-      </c>
-      <c r="H45">
-        <v>30</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D46" t="s">
-        <v>141</v>
-      </c>
-      <c r="E46">
-        <v>7.2</v>
-      </c>
-      <c r="F46">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>187</v>
-      </c>
-      <c r="H46">
-        <v>32</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D47" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E47">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H47">
-        <v>180</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D48" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E48">
-        <v>2.1</v>
+        <v>9.1</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H48">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D49" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E49">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H49">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D50" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E50">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H50">
         <v>180</v>
@@ -2186,51 +2183,51 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C51" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D51" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E51">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H51">
-        <v>896</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C52" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D52" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E52">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H52">
         <v>10</v>
@@ -2238,204 +2235,204 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C53" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D53" t="s">
-        <v>137</v>
+        <v>145</v>
+      </c>
+      <c r="E53">
+        <v>4.1</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H53">
-        <v>8</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C54" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D54" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E54">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="F54">
         <v>2</v>
       </c>
       <c r="G54" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H54">
-        <v>5</v>
+        <v>896</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E55">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="F55">
         <v>2</v>
       </c>
       <c r="G55" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H55">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C56" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
-      </c>
-      <c r="E56">
-        <v>7.1</v>
+        <v>143</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H56">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C57" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D57" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E57">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H57">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B58" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D58" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E58">
-        <v>4.1</v>
+        <v>7.1</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H58">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D59" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E59">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H59">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D60" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E60">
-        <v>5.2</v>
+        <v>2.1</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H60">
         <v>18</v>
@@ -2443,79 +2440,157 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D61" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E61">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H61">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D62" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E62">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H62">
-        <v>90</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" t="s">
+        <v>131</v>
+      </c>
+      <c r="C63" t="s">
+        <v>142</v>
+      </c>
+      <c r="D63" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63">
+        <v>5.2</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63" t="s">
+        <v>209</v>
+      </c>
+      <c r="H63">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
         <v>67</v>
       </c>
-      <c r="B63" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" t="s">
-        <v>136</v>
-      </c>
-      <c r="D63" t="s">
-        <v>140</v>
-      </c>
-      <c r="E63">
+      <c r="B64" t="s">
+        <v>132</v>
+      </c>
+      <c r="C64" t="s">
+        <v>142</v>
+      </c>
+      <c r="D64" t="s">
+        <v>145</v>
+      </c>
+      <c r="E64">
+        <v>5.2</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>210</v>
+      </c>
+      <c r="H64">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" t="s">
+        <v>142</v>
+      </c>
+      <c r="D65" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65">
+        <v>5.6</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65" t="s">
+        <v>211</v>
+      </c>
+      <c r="H65">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" t="s">
+        <v>142</v>
+      </c>
+      <c r="D66" t="s">
+        <v>145</v>
+      </c>
+      <c r="E66">
         <v>2.1</v>
       </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63" t="s">
-        <v>204</v>
-      </c>
-      <c r="H63">
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>212</v>
+      </c>
+      <c r="H66">
         <v>54</v>
       </c>
     </row>

--- a/target_df.xlsx
+++ b/target_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="213">
   <si>
     <t>Kürzel (LongName)</t>
   </si>
@@ -43,129 +43,129 @@
     <t>KOR</t>
   </si>
   <si>
+    <t>TRH</t>
+  </si>
+  <si>
+    <t>VRF</t>
+  </si>
+  <si>
+    <t>WIF</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>ASP</t>
+  </si>
+  <si>
+    <t>AVF</t>
+  </si>
+  <si>
+    <t>BUF</t>
+  </si>
+  <si>
+    <t>GAR</t>
+  </si>
+  <si>
+    <t>PAA</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>PAK</t>
+  </si>
+  <si>
+    <t>PPA</t>
+  </si>
+  <si>
+    <t>UUF</t>
+  </si>
+  <si>
+    <t>VEL_L</t>
+  </si>
+  <si>
+    <t>VEL_S</t>
+  </si>
+  <si>
+    <t>AUF_G</t>
+  </si>
+  <si>
+    <t>AUF_M</t>
+  </si>
+  <si>
+    <t>BLB</t>
+  </si>
+  <si>
+    <t>KUC</t>
+  </si>
+  <si>
+    <t>KUE</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>KUW</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>RKU</t>
+  </si>
+  <si>
+    <t>VOR</t>
+  </si>
+  <si>
+    <t>WCD</t>
+  </si>
+  <si>
+    <t>WCH</t>
+  </si>
+  <si>
+    <t>WCK</t>
+  </si>
+  <si>
+    <t>WCM</t>
+  </si>
+  <si>
+    <t>WCR</t>
+  </si>
+  <si>
+    <t>HTR_E</t>
+  </si>
+  <si>
+    <t>HTR_K</t>
+  </si>
+  <si>
+    <t>HTR_L</t>
+  </si>
+  <si>
+    <t>HTR_S</t>
+  </si>
+  <si>
+    <t>SCH</t>
+  </si>
+  <si>
+    <t>AGH</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>GRP</t>
+  </si>
+  <si>
+    <t>HRR</t>
+  </si>
+  <si>
+    <t>RRG</t>
+  </si>
+  <si>
     <t>LUF</t>
   </si>
   <si>
-    <t>TRH</t>
-  </si>
-  <si>
-    <t>VRF</t>
-  </si>
-  <si>
-    <t>WIF</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>ASP</t>
-  </si>
-  <si>
-    <t>AVF</t>
-  </si>
-  <si>
-    <t>BUF</t>
-  </si>
-  <si>
-    <t>GAR</t>
-  </si>
-  <si>
-    <t>PAA</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>PAK</t>
-  </si>
-  <si>
-    <t>PPA</t>
-  </si>
-  <si>
-    <t>UUF</t>
-  </si>
-  <si>
-    <t>VEL_L</t>
-  </si>
-  <si>
-    <t>VEL_S</t>
-  </si>
-  <si>
-    <t>AUF_G</t>
-  </si>
-  <si>
-    <t>AUF_M</t>
-  </si>
-  <si>
-    <t>BLB</t>
-  </si>
-  <si>
-    <t>KUC</t>
-  </si>
-  <si>
-    <t>KUE</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>KUW</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>RKU</t>
-  </si>
-  <si>
-    <t>VOR</t>
-  </si>
-  <si>
-    <t>WCD</t>
-  </si>
-  <si>
-    <t>WCH</t>
-  </si>
-  <si>
-    <t>WCK</t>
-  </si>
-  <si>
-    <t>WCM</t>
-  </si>
-  <si>
-    <t>WCR</t>
-  </si>
-  <si>
-    <t>HTR_E</t>
-  </si>
-  <si>
-    <t>HTR_K</t>
-  </si>
-  <si>
-    <t>HTR_L</t>
-  </si>
-  <si>
-    <t>HTR_S</t>
-  </si>
-  <si>
-    <t>SCH</t>
-  </si>
-  <si>
-    <t>AGH</t>
-  </si>
-  <si>
-    <t>CON</t>
-  </si>
-  <si>
-    <t>GRP</t>
-  </si>
-  <si>
-    <t>HRR</t>
-  </si>
-  <si>
-    <t>RRG</t>
-  </si>
-  <si>
     <t>ANF</t>
   </si>
   <si>
@@ -229,129 +229,129 @@
     <t>Korridor</t>
   </si>
   <si>
+    <t>Treppenhaus</t>
+  </si>
+  <si>
+    <t>Verkehrsfläche</t>
+  </si>
+  <si>
+    <t>Windfang</t>
+  </si>
+  <si>
+    <t>Allwetterplatz mit Sportbelag</t>
+  </si>
+  <si>
+    <t>Aussensitzplatz Mensa/Verpflegung</t>
+  </si>
+  <si>
+    <t>Zufahrt, Abstandsfläche, Umschwung</t>
+  </si>
+  <si>
+    <t>Bearbeitet Umgebungsflächen</t>
+  </si>
+  <si>
+    <t>Schulgarten</t>
+  </si>
+  <si>
+    <t>Pausenfläche PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gedeckter Aussenbereich </t>
+  </si>
+  <si>
+    <t>Aussenraum Kindergarten</t>
+  </si>
+  <si>
+    <t>Parkplätze PW (Normbedarf)</t>
+  </si>
+  <si>
+    <t>Unbearbeitete Umgebungsflächen</t>
+  </si>
+  <si>
+    <t>Velo- Abstellplätze Schulpersonal</t>
+  </si>
+  <si>
+    <t>Velo- Abstellplätze Schulkinder</t>
+  </si>
+  <si>
+    <t>Aufenthaltsraum gross</t>
+  </si>
+  <si>
+    <t>Aufenthaltsraum mittel</t>
+  </si>
+  <si>
+    <t>Leitung Betreuung</t>
+  </si>
+  <si>
+    <t>Küche</t>
+  </si>
+  <si>
+    <t>Küche Entsorgung</t>
+  </si>
+  <si>
+    <t>Lager non-food</t>
+  </si>
+  <si>
+    <t>Küche Wagenbahnhof/-park (Rollboys)</t>
+  </si>
+  <si>
+    <t>Mensa PS</t>
+  </si>
+  <si>
+    <t>Reinigung und Wäsche Küche</t>
+  </si>
+  <si>
+    <t>Vorzone Klassenzimmer</t>
+  </si>
+  <si>
+    <t>WC Schulpersonal D</t>
+  </si>
+  <si>
+    <t>WC Schulpersonal H</t>
+  </si>
+  <si>
+    <t>WC SuS Knaben</t>
+  </si>
+  <si>
+    <t>WC SuS Mädchen</t>
+  </si>
+  <si>
+    <t>WC Rollstuhlgerecht (genderneutral)</t>
+  </si>
+  <si>
+    <t>Elektohauptverteilung</t>
+  </si>
+  <si>
+    <t>Heizung (+ Kälte)</t>
+  </si>
+  <si>
+    <t>Lüftung</t>
+  </si>
+  <si>
+    <t>Sanitär</t>
+  </si>
+  <si>
+    <t>Schacht</t>
+  </si>
+  <si>
+    <t>Aussengerätraum LHT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Containerraum </t>
+  </si>
+  <si>
+    <t>Garderobe / Personalraum</t>
+  </si>
+  <si>
+    <t>Hauptreinigungsraum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reinigungsraum Geschoss </t>
+  </si>
+  <si>
     <t>Luftraum</t>
   </si>
   <si>
-    <t>Treppenhaus</t>
-  </si>
-  <si>
-    <t>Verkehrsfläche</t>
-  </si>
-  <si>
-    <t>Windfang</t>
-  </si>
-  <si>
-    <t>Allwetterplatz mit Sportbelag</t>
-  </si>
-  <si>
-    <t>Aussensitzplatz Mensa/Verpflegung</t>
-  </si>
-  <si>
-    <t>Zufahrt, Abstandsfläche, Umschwung</t>
-  </si>
-  <si>
-    <t>Bearbeitet Umgebungsflächen</t>
-  </si>
-  <si>
-    <t>Schulgarten</t>
-  </si>
-  <si>
-    <t>Pausenfläche PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gedeckter Aussenbereich </t>
-  </si>
-  <si>
-    <t>Aussenraum Kindergarten</t>
-  </si>
-  <si>
-    <t>Parkplätze PW (Normbedarf)</t>
-  </si>
-  <si>
-    <t>Unbearbeitete Umgebungsflächen</t>
-  </si>
-  <si>
-    <t>Velo- Abstellplätze Schulpersonal</t>
-  </si>
-  <si>
-    <t>Velo- Abstellplätze Schulkinder</t>
-  </si>
-  <si>
-    <t>Aufenthaltsraum gross</t>
-  </si>
-  <si>
-    <t>Aufenthaltsraum mittel</t>
-  </si>
-  <si>
-    <t>Leitung Betreuung</t>
-  </si>
-  <si>
-    <t>Küche</t>
-  </si>
-  <si>
-    <t>Küche Entsorgung</t>
-  </si>
-  <si>
-    <t>Lager non-food</t>
-  </si>
-  <si>
-    <t>Küche Wagenbahnhof/-park (Rollboys)</t>
-  </si>
-  <si>
-    <t>Mensa PS</t>
-  </si>
-  <si>
-    <t>Reinigung und Wäsche Küche</t>
-  </si>
-  <si>
-    <t>Vorzone Klassenzimmer</t>
-  </si>
-  <si>
-    <t>WC Schulpersonal D</t>
-  </si>
-  <si>
-    <t>WC Schulpersonal H</t>
-  </si>
-  <si>
-    <t>WC SuS Knaben</t>
-  </si>
-  <si>
-    <t>WC SuS Mädchen</t>
-  </si>
-  <si>
-    <t>WC Rollstuhlgerecht (genderneutral)</t>
-  </si>
-  <si>
-    <t>Elektohauptverteilung</t>
-  </si>
-  <si>
-    <t>Heizung (+ Kälte)</t>
-  </si>
-  <si>
-    <t>Lüftung</t>
-  </si>
-  <si>
-    <t>Sanitär</t>
-  </si>
-  <si>
-    <t>Schacht</t>
-  </si>
-  <si>
-    <t>Aussengerätraum LHT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Containerraum </t>
-  </si>
-  <si>
-    <t>Garderobe / Personalraum</t>
-  </si>
-  <si>
-    <t>Hauptreinigungsraum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reinigungsraum Geschoss </t>
-  </si>
-  <si>
     <t>Aussennutzfläche</t>
   </si>
   <si>
@@ -463,9 +463,6 @@
     <t>Allgemein_KOR</t>
   </si>
   <si>
-    <t>Allgemein_LUF</t>
-  </si>
-  <si>
     <t>Allgemein_TRH</t>
   </si>
   <si>
@@ -584,6 +581,9 @@
   </si>
   <si>
     <t>Hausdienst_RRG</t>
+  </si>
+  <si>
+    <t>Luftraum_LUF</t>
   </si>
   <si>
     <t>Sonstige Umgebung_ANF</t>
@@ -1066,6 +1066,9 @@
       <c r="C3" t="s">
         <v>135</v>
       </c>
+      <c r="D3" t="s">
+        <v>143</v>
+      </c>
       <c r="G3" t="s">
         <v>149</v>
       </c>
@@ -1112,13 +1115,22 @@
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>10.4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>152</v>
+      </c>
+      <c r="H6">
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1132,7 +1144,7 @@
         <v>136</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E7">
         <v>10.4</v>
@@ -1144,7 +1156,7 @@
         <v>153</v>
       </c>
       <c r="H7">
-        <v>390</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1158,19 +1170,10 @@
         <v>136</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>10.4</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
         <v>154</v>
-      </c>
-      <c r="H8">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1184,7 +1187,7 @@
         <v>136</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
         <v>155</v>
@@ -1201,7 +1204,7 @@
         <v>136</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
         <v>156</v>
@@ -1217,8 +1220,20 @@
       <c r="C11" t="s">
         <v>136</v>
       </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11">
+        <v>10.8</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
       <c r="G11" t="s">
         <v>157</v>
+      </c>
+      <c r="H11">
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1232,10 +1247,7 @@
         <v>136</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12">
-        <v>10.8</v>
+        <v>144</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1244,7 +1256,7 @@
         <v>158</v>
       </c>
       <c r="H12">
-        <v>400</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1258,16 +1270,19 @@
         <v>136</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>10.8</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="s">
         <v>159</v>
       </c>
       <c r="H13">
-        <v>54</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1281,19 +1296,19 @@
         <v>136</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="s">
         <v>160</v>
       </c>
       <c r="H14">
-        <v>300</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1307,19 +1322,10 @@
         <v>136</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15">
-        <v>10.1</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
         <v>161</v>
-      </c>
-      <c r="H15">
-        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1333,7 +1339,10 @@
         <v>136</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="E16">
+        <v>10.1</v>
       </c>
       <c r="G16" t="s">
         <v>162</v>
@@ -1350,7 +1359,7 @@
         <v>136</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17">
         <v>10.1</v>
@@ -1367,16 +1376,22 @@
         <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>145</v>
       </c>
       <c r="E18">
-        <v>10.1</v>
+        <v>1.2</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
       </c>
       <c r="G18" t="s">
         <v>164</v>
+      </c>
+      <c r="H18">
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1402,7 +1417,7 @@
         <v>165</v>
       </c>
       <c r="H19">
-        <v>72</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1419,7 +1434,7 @@
         <v>145</v>
       </c>
       <c r="E20">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1428,7 +1443,7 @@
         <v>166</v>
       </c>
       <c r="H20">
-        <v>54</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1445,7 +1460,7 @@
         <v>145</v>
       </c>
       <c r="E21">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1454,7 +1469,7 @@
         <v>167</v>
       </c>
       <c r="H21">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1471,7 +1486,7 @@
         <v>145</v>
       </c>
       <c r="E22">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1480,7 +1495,7 @@
         <v>168</v>
       </c>
       <c r="H22">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1506,7 +1521,7 @@
         <v>169</v>
       </c>
       <c r="H23">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1523,7 +1538,7 @@
         <v>145</v>
       </c>
       <c r="E24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1532,7 +1547,7 @@
         <v>170</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1549,7 +1564,7 @@
         <v>145</v>
       </c>
       <c r="E25">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1558,7 +1573,7 @@
         <v>171</v>
       </c>
       <c r="H25">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1572,10 +1587,10 @@
         <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1584,7 +1599,7 @@
         <v>172</v>
       </c>
       <c r="H26">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1601,7 +1616,7 @@
         <v>146</v>
       </c>
       <c r="E27">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -1610,7 +1625,7 @@
         <v>173</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1627,7 +1642,7 @@
         <v>146</v>
       </c>
       <c r="E28">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -1636,7 +1651,7 @@
         <v>174</v>
       </c>
       <c r="H28">
-        <v>108</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1740,7 +1755,7 @@
         <v>178</v>
       </c>
       <c r="H32">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1751,13 +1766,13 @@
         <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E33">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1766,7 +1781,7 @@
         <v>179</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1783,16 +1798,16 @@
         <v>147</v>
       </c>
       <c r="E34">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="s">
         <v>180</v>
       </c>
       <c r="H34">
-        <v>25</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1809,16 +1824,16 @@
         <v>147</v>
       </c>
       <c r="E35">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="s">
         <v>181</v>
       </c>
       <c r="H35">
-        <v>90</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1835,7 +1850,7 @@
         <v>147</v>
       </c>
       <c r="E36">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -1844,7 +1859,7 @@
         <v>182</v>
       </c>
       <c r="H36">
-        <v>150</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1860,9 +1875,6 @@
       <c r="D37" t="s">
         <v>147</v>
       </c>
-      <c r="E37">
-        <v>8.300000000000001</v>
-      </c>
       <c r="F37">
         <v>1</v>
       </c>
@@ -1870,7 +1882,7 @@
         <v>183</v>
       </c>
       <c r="H37">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1881,10 +1893,13 @@
         <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="E38">
+        <v>4.1</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -1893,7 +1908,7 @@
         <v>184</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1910,7 +1925,7 @@
         <v>146</v>
       </c>
       <c r="E39">
-        <v>4.1</v>
+        <v>7.3</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -1919,7 +1934,7 @@
         <v>185</v>
       </c>
       <c r="H39">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1936,7 +1951,7 @@
         <v>146</v>
       </c>
       <c r="E40">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -1962,7 +1977,7 @@
         <v>146</v>
       </c>
       <c r="E41">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -1971,7 +1986,7 @@
         <v>187</v>
       </c>
       <c r="H41">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1991,13 +2006,13 @@
         <v>7.1</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42" t="s">
         <v>188</v>
       </c>
       <c r="H42">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2008,22 +2023,13 @@
         <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43">
-        <v>7.1</v>
-      </c>
-      <c r="F43">
-        <v>3</v>
+        <v>111</v>
       </c>
       <c r="G43" t="s">
         <v>189</v>
-      </c>
-      <c r="H43">
-        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2045,7 +2051,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B45" t="s">
         <v>113</v>
@@ -2054,7 +2060,7 @@
         <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G45" t="s">
         <v>191</v>
@@ -2071,7 +2077,7 @@
         <v>140</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46" t="s">
         <v>192</v>
@@ -2336,7 +2342,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B57" t="s">
         <v>125</v>
@@ -2362,7 +2368,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B58" t="s">
         <v>126</v>
